--- a/DSSV_TIN4403.008.xlsx
+++ b/DSSV_TIN4403.008.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\CNTT\TIN4403_LTDD\2025-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Laptrinhungdungdidong\2025-2026.1.TIN4403.008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE325F00-FCE3-46FA-B603-73AB064F1715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="2100" yWindow="1575" windowWidth="31620" windowHeight="17685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="2100" yWindow="1580" windowWidth="31620" windowHeight="17690" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DANHSACHSINHVIEN" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1265,7 +1264,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1315,15 +1314,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F61" totalsRowShown="0">
-  <autoFilter ref="A1:F61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F61" totalsRowShown="0">
+  <autoFilter ref="A1:F61"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Mã sinh viên"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Họ"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tên"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Ngày sinh"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Khóa học"/>
+    <tableColumn id="1" name="STT"/>
+    <tableColumn id="2" name="Mã sinh viên"/>
+    <tableColumn id="3" name="Họ"/>
+    <tableColumn id="4" name="Tên"/>
+    <tableColumn id="5" name="Ngày sinh"/>
+    <tableColumn id="6" name="Khóa học"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1613,29 +1612,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" customWidth="1"/>
+    <col min="4" max="4" width="7.453125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" customWidth="1"/>
-    <col min="21" max="21" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" customWidth="1"/>
+    <col min="17" max="17" width="8.26953125" customWidth="1"/>
+    <col min="18" max="18" width="12.453125" customWidth="1"/>
+    <col min="19" max="19" width="12.81640625" customWidth="1"/>
+    <col min="21" max="21" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1655,7 +1654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1811,7 +1810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1889,7 +1888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1967,7 +1966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2045,7 +2044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2201,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2591,7 +2590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2747,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2903,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2981,7 +2980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3215,7 +3214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3293,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3605,7 +3604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3683,7 +3682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3761,7 +3760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3839,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3917,7 +3916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3995,7 +3994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4073,7 +4072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4151,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4229,7 +4228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4307,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4385,7 +4384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4463,7 +4462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4541,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4619,7 +4618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4697,7 +4696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4775,7 +4774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4853,7 +4852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4931,7 +4930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5009,7 +5008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5087,7 +5086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5165,7 +5164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5243,7 +5242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5321,7 +5320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5399,7 +5398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5477,7 +5476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5555,7 +5554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5633,7 +5632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5711,7 +5710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5789,7 +5788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5867,7 +5866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5945,7 +5944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6023,7 +6022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6101,7 +6100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6179,7 +6178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6257,7 +6256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6345,11 +6344,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B479F7-B41C-46F3-B023-1FB06BE6104B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>291</v>
       </c>
@@ -6360,7 +6359,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>244</v>
       </c>
@@ -6371,7 +6370,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>245</v>
       </c>
@@ -6382,7 +6381,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>246</v>
       </c>
@@ -6393,7 +6392,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>247</v>
       </c>
@@ -6404,7 +6403,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>248</v>
       </c>
@@ -6415,7 +6414,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>249</v>
       </c>
@@ -6426,7 +6425,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>231</v>
       </c>
@@ -6437,7 +6436,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -6448,7 +6447,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>251</v>
       </c>
@@ -6459,7 +6458,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>252</v>
       </c>
@@ -6470,7 +6469,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>253</v>
       </c>
@@ -6481,7 +6480,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>255</v>
       </c>
@@ -6503,7 +6502,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>256</v>
       </c>
@@ -6514,7 +6513,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>257</v>
       </c>
@@ -6525,7 +6524,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>258</v>
       </c>
@@ -6536,7 +6535,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>232</v>
       </c>
@@ -6547,7 +6546,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>259</v>
       </c>
@@ -6558,7 +6557,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>233</v>
       </c>
@@ -6569,7 +6568,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>260</v>
       </c>
@@ -6580,7 +6579,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>261</v>
       </c>
@@ -6591,7 +6590,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -6602,7 +6601,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>263</v>
       </c>
@@ -6613,7 +6612,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>234</v>
       </c>
@@ -6624,7 +6623,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>264</v>
       </c>
@@ -6635,7 +6634,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>235</v>
       </c>
@@ -6646,7 +6645,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>236</v>
       </c>
@@ -6657,7 +6656,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>265</v>
       </c>
@@ -6668,7 +6667,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>266</v>
       </c>
@@ -6679,7 +6678,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>237</v>
       </c>
@@ -6690,7 +6689,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>238</v>
       </c>
@@ -6701,7 +6700,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>239</v>
       </c>
@@ -6712,7 +6711,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>267</v>
       </c>
@@ -6723,7 +6722,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>268</v>
       </c>
@@ -6734,7 +6733,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>269</v>
       </c>
@@ -6745,7 +6744,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>270</v>
       </c>
@@ -6756,7 +6755,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>271</v>
       </c>
@@ -6767,7 +6766,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>272</v>
       </c>
@@ -6778,7 +6777,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>273</v>
       </c>
@@ -6789,7 +6788,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>240</v>
       </c>
@@ -6800,7 +6799,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>274</v>
       </c>
@@ -6811,7 +6810,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>275</v>
       </c>
@@ -6822,7 +6821,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>241</v>
       </c>
@@ -6833,7 +6832,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>276</v>
       </c>
@@ -6844,7 +6843,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>277</v>
       </c>
@@ -6855,7 +6854,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>242</v>
       </c>
@@ -6866,7 +6865,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>278</v>
       </c>
@@ -6877,7 +6876,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>279</v>
       </c>
@@ -6888,7 +6887,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>280</v>
       </c>
@@ -6899,7 +6898,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>281</v>
       </c>
@@ -6910,7 +6909,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>282</v>
       </c>
@@ -6921,7 +6920,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>243</v>
       </c>
@@ -6932,7 +6931,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>283</v>
       </c>
@@ -6943,7 +6942,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>284</v>
       </c>
@@ -6954,7 +6953,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>290</v>
       </c>
@@ -6965,7 +6964,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>285</v>
       </c>
@@ -6976,7 +6975,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>286</v>
       </c>
@@ -6987,7 +6986,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>287</v>
       </c>
@@ -6998,7 +6997,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>288</v>
       </c>
@@ -7009,7 +7008,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>289</v>
       </c>
